--- a/data/trans_orig/P16A03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A03-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21831</t>
+          <t>22337</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30020</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55370</t>
+          <t>54949</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40882</t>
+          <t>41591</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69923</t>
+          <t>69859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>671163</t>
+          <t>670657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>685279</t>
+          <t>685417</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>632981</t>
+          <t>633402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>658331</t>
+          <t>658387</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1311422</t>
+          <t>1311486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1340463</t>
+          <t>1339754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15455</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>36118</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38603</t>
+          <t>40568</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68176</t>
+          <t>70534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60590</t>
+          <t>60798</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97278</t>
+          <t>96052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>923023</t>
+          <t>925682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>946345</t>
+          <t>947964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>900217</t>
+          <t>897859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>929790</t>
+          <t>927825</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1832915</t>
+          <t>1834141</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1869603</t>
+          <t>1869395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>21907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26501</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49511</t>
+          <t>49470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35811</t>
+          <t>35147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64925</t>
+          <t>63580</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>657649</t>
+          <t>656602</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673695</t>
+          <t>672925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>634330</t>
+          <t>634371</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657340</t>
+          <t>658192</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1297425</t>
+          <t>1298770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1326539</t>
+          <t>1327203</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>16537</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35383</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>36343</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62900</t>
+          <t>64475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58061</t>
+          <t>58736</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90903</t>
+          <t>91221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>906839</t>
+          <t>907531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>925227</t>
+          <t>925685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>975712</t>
+          <t>974137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1002835</t>
+          <t>1002269</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1889931</t>
+          <t>1889613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1922773</t>
+          <t>1922098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58615</t>
+          <t>57390</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94985</t>
+          <t>91669</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>154672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204663</t>
+          <t>206254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220429</t>
+          <t>222735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>281987</t>
+          <t>286084</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3180540</t>
+          <t>3183856</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3216910</t>
+          <t>3218135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3174534</t>
+          <t>3172943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3225050</t>
+          <t>3224525</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6372735</t>
+          <t>6368638</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6434293</t>
+          <t>6431987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25727</t>
+          <t>26921</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51277</t>
+          <t>50674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31525</t>
+          <t>30842</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57743</t>
+          <t>57865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>688836</t>
+          <t>688174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>698077</t>
+          <t>698152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641060</t>
+          <t>641663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>666610</t>
+          <t>665416</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1335357</t>
+          <t>1335235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1361575</t>
+          <t>1362258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20709</t>
+          <t>20585</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52634</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85004</t>
+          <t>86672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61251</t>
+          <t>61610</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98355</t>
+          <t>97796</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>997238</t>
+          <t>997362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1011754</t>
+          <t>1011402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>942771</t>
+          <t>941103</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>975141</t>
+          <t>975474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1947368</t>
+          <t>1947927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1984472</t>
+          <t>1984113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34144</t>
+          <t>34457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62944</t>
+          <t>63796</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45013</t>
+          <t>45708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78173</t>
+          <t>78611</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>732109</t>
+          <t>731478</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>751370</t>
+          <t>750997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>713339</t>
+          <t>712487</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>742139</t>
+          <t>741826</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1454648</t>
+          <t>1454210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1487808</t>
+          <t>1487113</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>26357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47688</t>
+          <t>46323</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79343</t>
+          <t>80942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58620</t>
+          <t>59326</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97025</t>
+          <t>96116</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>919309</t>
+          <t>917582</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>935116</t>
+          <t>934558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>968355</t>
+          <t>966756</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1000010</t>
+          <t>1001375</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1894612</t>
+          <t>1895521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1933017</t>
+          <t>1932311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34073</t>
+          <t>32689</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61591</t>
+          <t>62370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185300</t>
+          <t>185266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243332</t>
+          <t>243139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227342</t>
+          <t>228931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>292577</t>
+          <t>294050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3357597</t>
+          <t>3356818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3385115</t>
+          <t>3386499</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3300762</t>
+          <t>3300955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3358794</t>
+          <t>3358828</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6670705</t>
+          <t>6669232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6735940</t>
+          <t>6734351</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>11172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24536</t>
+          <t>23852</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46813</t>
+          <t>47781</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28155</t>
+          <t>28514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51940</t>
+          <t>53090</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664052</t>
+          <t>663628</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673135</t>
+          <t>672882</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>626026</t>
+          <t>625058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>648303</t>
+          <t>648987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1295699</t>
+          <t>1294549</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1319484</t>
+          <t>1319125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22185</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44743</t>
+          <t>47018</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31803</t>
+          <t>33231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59381</t>
+          <t>60467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1002273</t>
+          <t>1000904</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1015692</t>
+          <t>1015946</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>998170</t>
+          <t>995895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1020728</t>
+          <t>1021203</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2005963</t>
+          <t>2004877</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2033541</t>
+          <t>2032113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20411</t>
+          <t>21474</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42530</t>
+          <t>42816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30072</t>
+          <t>30040</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55251</t>
+          <t>57082</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739141</t>
+          <t>738078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753617</t>
+          <t>753522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>742481</t>
+          <t>742195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>764587</t>
+          <t>763935</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1489312</t>
+          <t>1487481</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1514491</t>
+          <t>1514523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23913</t>
+          <t>23696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36197</t>
+          <t>37360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67175</t>
+          <t>66157</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50813</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>84128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>913654</t>
+          <t>913871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>928936</t>
+          <t>928890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>976604</t>
+          <t>977622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1007582</t>
+          <t>1006419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1898656</t>
+          <t>1897218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1930533</t>
+          <t>1931366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31640</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58547</t>
+          <t>58279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123591</t>
+          <t>122626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172901</t>
+          <t>175335</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>162858</t>
+          <t>166431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>218963</t>
+          <t>217995</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3335803</t>
+          <t>3336071</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3362710</t>
+          <t>3361436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3371641</t>
+          <t>3369207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3420951</t>
+          <t>3421916</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6719929</t>
+          <t>6720897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6776034</t>
+          <t>6772461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11782</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27628</t>
+          <t>26786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36812</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59248</t>
+          <t>58821</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>607323</t>
+          <t>608165</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>623169</t>
+          <t>624244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>638610</t>
+          <t>637016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>652521</t>
+          <t>651881</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1251125</t>
+          <t>1251552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1272260</t>
+          <t>1272448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25521</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34052</t>
+          <t>34684</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55500</t>
+          <t>54436</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38626</t>
+          <t>39377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74683</t>
+          <t>74499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1167343</t>
+          <t>1166849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1185927</t>
+          <t>1185698</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>902606</t>
+          <t>903670</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>924054</t>
+          <t>923422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2076288</t>
+          <t>2076472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2112345</t>
+          <t>2111594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46163</t>
+          <t>45331</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31819</t>
+          <t>30393</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63733</t>
+          <t>62009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>678278</t>
+          <t>678735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>693993</t>
+          <t>693789</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>886637</t>
+          <t>887469</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>916645</t>
+          <t>917507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1572751</t>
+          <t>1574475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1604665</t>
+          <t>1606091</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29607</t>
+          <t>30584</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58548</t>
+          <t>58161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93422</t>
+          <t>91309</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78293</t>
+          <t>76585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115131</t>
+          <t>113630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>897224</t>
+          <t>896247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>914715</t>
+          <t>914227</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>997952</t>
+          <t>1000065</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1032826</t>
+          <t>1033213</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1903074</t>
+          <t>1904575</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1939912</t>
+          <t>1941620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50926</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86019</t>
+          <t>87804</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148904</t>
+          <t>149245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206724</t>
+          <t>208661</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212144</t>
+          <t>215097</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>284391</t>
+          <t>282375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3372311</t>
+          <t>3370526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3407404</t>
+          <t>3406662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3450978</t>
+          <t>3449041</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3508798</t>
+          <t>3508457</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6831641</t>
+          <t>6833657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6903888</t>
+          <t>6900935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A03-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22337</t>
+          <t>22531</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29964</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54949</t>
+          <t>54377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>40978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69859</t>
+          <t>69070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>670657</t>
+          <t>670463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>685417</t>
+          <t>686043</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>633402</t>
+          <t>633974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>658387</t>
+          <t>658623</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1311486</t>
+          <t>1312275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1339754</t>
+          <t>1340367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>14686</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36118</t>
+          <t>36736</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40568</t>
+          <t>38999</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70534</t>
+          <t>69333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60798</t>
+          <t>59922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96052</t>
+          <t>97660</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>925682</t>
+          <t>925064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>947964</t>
+          <t>947114</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>897859</t>
+          <t>899060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>927825</t>
+          <t>929394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1834141</t>
+          <t>1832533</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1869395</t>
+          <t>1870271</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21907</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>26863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49470</t>
+          <t>51624</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35147</t>
+          <t>34890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63580</t>
+          <t>63203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656602</t>
+          <t>657979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>672925</t>
+          <t>673192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>634371</t>
+          <t>632217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>658192</t>
+          <t>656978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1298770</t>
+          <t>1299147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327203</t>
+          <t>1327460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16537</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>36459</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36343</t>
+          <t>36988</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64475</t>
+          <t>63634</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58736</t>
+          <t>58671</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91221</t>
+          <t>90928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>907531</t>
+          <t>905763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>925685</t>
+          <t>924752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>974137</t>
+          <t>974978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1002269</t>
+          <t>1001624</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1889613</t>
+          <t>1889906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1922098</t>
+          <t>1922163</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57390</t>
+          <t>56909</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91669</t>
+          <t>93723</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154672</t>
+          <t>152853</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206254</t>
+          <t>207030</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>222735</t>
+          <t>224272</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>286084</t>
+          <t>290756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3183856</t>
+          <t>3181802</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3218135</t>
+          <t>3218616</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3172943</t>
+          <t>3172167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3224525</t>
+          <t>3226344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6368638</t>
+          <t>6363966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6431987</t>
+          <t>6430450</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>11749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26921</t>
+          <t>26356</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50674</t>
+          <t>49666</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30842</t>
+          <t>32513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57865</t>
+          <t>58701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>688174</t>
+          <t>689015</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>698152</t>
+          <t>698712</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641663</t>
+          <t>642671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>665416</t>
+          <t>665981</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1335235</t>
+          <t>1334399</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1362258</t>
+          <t>1360587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20585</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52301</t>
+          <t>51977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86672</t>
+          <t>85768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61610</t>
+          <t>61167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97796</t>
+          <t>100409</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>997362</t>
+          <t>997661</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1011402</t>
+          <t>1011917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>941103</t>
+          <t>942007</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>975474</t>
+          <t>975798</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1947927</t>
+          <t>1945314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1984113</t>
+          <t>1984556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>24856</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34457</t>
+          <t>33846</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63796</t>
+          <t>62603</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45708</t>
+          <t>45135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78611</t>
+          <t>79225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>731478</t>
+          <t>731682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>750997</t>
+          <t>751123</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>712487</t>
+          <t>713680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>741826</t>
+          <t>742437</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1454210</t>
+          <t>1453596</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1487113</t>
+          <t>1487686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46323</t>
+          <t>46262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80942</t>
+          <t>78222</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59326</t>
+          <t>61813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96116</t>
+          <t>97691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>917582</t>
+          <t>918328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934558</t>
+          <t>935087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>966756</t>
+          <t>969476</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1001375</t>
+          <t>1001436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1895521</t>
+          <t>1893946</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1932311</t>
+          <t>1929824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32689</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62370</t>
+          <t>62408</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185266</t>
+          <t>184917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243139</t>
+          <t>244436</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>228931</t>
+          <t>227027</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>294050</t>
+          <t>293901</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3356818</t>
+          <t>3356780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3386499</t>
+          <t>3387292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3300955</t>
+          <t>3299658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3358828</t>
+          <t>3359177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6669232</t>
+          <t>6669381</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6734351</t>
+          <t>6736255</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>11079</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>23258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47781</t>
+          <t>47939</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>29072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53090</t>
+          <t>54604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>663628</t>
+          <t>663721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>672882</t>
+          <t>672907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>625058</t>
+          <t>624900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>648987</t>
+          <t>649581</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1294549</t>
+          <t>1293035</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1319125</t>
+          <t>1318567</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21527</t>
+          <t>19995</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>22330</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47018</t>
+          <t>46177</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33231</t>
+          <t>31702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60467</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1000904</t>
+          <t>1002436</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1015946</t>
+          <t>1016463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>995895</t>
+          <t>996736</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1021203</t>
+          <t>1020583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2004877</t>
+          <t>2005663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2032113</t>
+          <t>2033642</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21474</t>
+          <t>20941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>21772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42816</t>
+          <t>43595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30040</t>
+          <t>30399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57082</t>
+          <t>55947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>738078</t>
+          <t>738611</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753522</t>
+          <t>753723</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>742195</t>
+          <t>741416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>763935</t>
+          <t>763239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1487481</t>
+          <t>1488616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1514523</t>
+          <t>1514164</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23696</t>
+          <t>24325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37360</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66157</t>
+          <t>66807</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49980</t>
+          <t>48985</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84128</t>
+          <t>81389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>913871</t>
+          <t>913242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>928890</t>
+          <t>928738</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>977622</t>
+          <t>976972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1006419</t>
+          <t>1007179</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1897218</t>
+          <t>1899957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1931366</t>
+          <t>1932361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32914</t>
+          <t>32060</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58279</t>
+          <t>56894</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>122626</t>
+          <t>123306</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>175335</t>
+          <t>171513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>166431</t>
+          <t>165567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>217995</t>
+          <t>219283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3336071</t>
+          <t>3337456</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3361436</t>
+          <t>3362290</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3369207</t>
+          <t>3373029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3421916</t>
+          <t>3421236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6720897</t>
+          <t>6719609</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6772461</t>
+          <t>6773325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>29846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29974</t>
+          <t>31922</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>24683</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>40529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,27 +6639,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>47390</t>
+          <t>50767</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>40689</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58821</t>
+          <t>63839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>617535</t>
+          <t>671370</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>608165</t>
+          <t>660369</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>624244</t>
+          <t>678161</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>645448</t>
+          <t>700860</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>637016</t>
+          <t>692253</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>651881</t>
+          <t>708099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,22 +6752,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1262983</t>
+          <t>1372230</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1251552</t>
+          <t>1359158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1272448</t>
+          <t>1382308</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26015</t>
+          <t>25964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44037</t>
+          <t>48289</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34684</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54436</t>
+          <t>59761</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>59890</t>
+          <t>65104</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39377</t>
+          <t>52761</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74499</t>
+          <t>79203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1177011</t>
+          <t>1032102</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1166849</t>
+          <t>1022953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1185698</t>
+          <t>1038043</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>914069</t>
+          <t>1022549</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>903670</t>
+          <t>1011077</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>923422</t>
+          <t>1032519</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2091081</t>
+          <t>2054651</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2076472</t>
+          <t>2040552</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2111594</t>
+          <t>2066994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16045</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24949</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32086</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15293</t>
+          <t>29885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45331</t>
+          <t>52209</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48131</t>
+          <t>60458</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30393</t>
+          <t>47611</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62009</t>
+          <t>77827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>687639</t>
+          <t>780727</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>678735</t>
+          <t>768571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>693789</t>
+          <t>789761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>900714</t>
+          <t>772565</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>887469</t>
+          <t>759454</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>917507</t>
+          <t>781778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1588353</t>
+          <t>1553290</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1574475</t>
+          <t>1535921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1606091</t>
+          <t>1566137</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30584</t>
+          <t>31169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>75072</t>
+          <t>80825</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58161</t>
+          <t>66468</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91309</t>
+          <t>97094</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>94633</t>
+          <t>100846</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76585</t>
+          <t>84882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113630</t>
+          <t>120968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>907269</t>
+          <t>970041</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896247</t>
+          <t>958893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>914227</t>
+          <t>976909</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1016302</t>
+          <t>1036206</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1000065</t>
+          <t>1019937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1033213</t>
+          <t>1050563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1923572</t>
+          <t>2006247</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1904575</t>
+          <t>1986125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1941620</t>
+          <t>2022211</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>68876</t>
+          <t>77041</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>60192</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87804</t>
+          <t>93936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>181169</t>
+          <t>200134</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149245</t>
+          <t>178432</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>208661</t>
+          <t>226139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>250045</t>
+          <t>277175</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>215097</t>
+          <t>249208</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282375</t>
+          <t>307629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3389454</t>
+          <t>3454239</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3370526</t>
+          <t>3437344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3406662</t>
+          <t>3471088</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3476533</t>
+          <t>3532179</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3449041</t>
+          <t>3506174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3508457</t>
+          <t>3553881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6865987</t>
+          <t>6986418</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6833657</t>
+          <t>6955964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6900935</t>
+          <t>7014385</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
